--- a/nr-update-missing-fields/ig/StructureDefinition-as-ext-authorization.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-ext-authorization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1505" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="168">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T07:52:36+00:00</t>
+    <t>2024-07-17T09:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -505,102 +505,29 @@
     <t>Extension.extension:dateUpdateAuthorization.value[x]</t>
   </si>
   <si>
-    <t>Extension.extension:deleteAuthorization</t>
-  </si>
-  <si>
-    <t>deleteAuthorization</t>
+    <t>Extension.extension:deletedAuthorization</t>
+  </si>
+  <si>
+    <t>deletedAuthorization</t>
   </si>
   <si>
     <t>Indicateur de suppression de l'autorisation.</t>
   </si>
   <si>
-    <t>Extension.extension:deleteAuthorization.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:deleteAuthorization.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:deleteAuthorization.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:deleteAuthorization.value[x]</t>
+    <t>Extension.extension:deletedAuthorization.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:deletedAuthorization.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:deletedAuthorization.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:deletedAuthorization.value[x]</t>
   </si>
   <si>
     <t xml:space="preserve">boolean
 </t>
-  </si>
-  <si>
-    <t>Extension.extension:dateLastInstallation</t>
-  </si>
-  <si>
-    <t>dateLastInstallation</t>
-  </si>
-  <si>
-    <t>Date à laquelle le dernier constat d’installation des places est réalisé.</t>
-  </si>
-  <si>
-    <t>Extension.extension:dateLastInstallation.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:dateLastInstallation.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:dateLastInstallation.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:dateLastInstallation.value[x]</t>
-  </si>
-  <si>
-    <t>Extension.extension:deleteInstallation</t>
-  </si>
-  <si>
-    <t>deleteInstallation</t>
-  </si>
-  <si>
-    <t>Indicateur de suppression de l’installation.</t>
-  </si>
-  <si>
-    <t>Extension.extension:deleteInstallation.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:deleteInstallation.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:deleteInstallation.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:deleteInstallation.value[x]</t>
-  </si>
-  <si>
-    <t>Extension.extension:sourceReportInstallation</t>
-  </si>
-  <si>
-    <t>sourceReportInstallation</t>
-  </si>
-  <si>
-    <t>Source ayant permis le constat d'installation.</t>
-  </si>
-  <si>
-    <t>Extension.extension:sourceReportInstallation.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:sourceReportInstallation.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:sourceReportInstallation.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:sourceReportInstallation.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/VS-TRE-R301-SourceInformationInstallation</t>
   </si>
   <si>
     <t>base64Binary
@@ -922,7 +849,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK45"/>
+  <dimension ref="A1:AK30"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="55.9921875" customWidth="true" bestFit="true"/>
@@ -950,7 +877,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="92.07421875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="19.625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -3885,20 +3812,18 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>167</v>
+        <v>115</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>84</v>
@@ -3913,22 +3838,24 @@
         <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>169</v>
+        <v>112</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>77</v>
+        <v>3</v>
       </c>
       <c r="S29" t="s" s="2">
         <v>77</v>
@@ -3970,30 +3897,30 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>170</v>
+        <v>121</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4004,7 +3931,7 @@
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>77</v>
@@ -4016,13 +3943,13 @@
         <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>85</v>
+        <v>167</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>87</v>
+        <v>120</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4073,7 +4000,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4082,1567 +4009,12 @@
         <v>84</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="C31" s="2"/>
-      <c r="D31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E31" s="2"/>
-      <c r="F31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K31" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
-      <c r="P31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q31" s="2"/>
-      <c r="R31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AG31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK31" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="C32" s="2"/>
-      <c r="D32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E32" s="2"/>
-      <c r="F32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="G32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K32" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O32" s="2"/>
-      <c r="P32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q32" s="2"/>
-      <c r="R32" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="S32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="C33" s="2"/>
-      <c r="D33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E33" s="2"/>
-      <c r="F33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K33" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
-      <c r="P33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q33" s="2"/>
-      <c r="R33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AG33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AK33" t="s" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="D34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E34" s="2"/>
-      <c r="F34" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K34" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="L34" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
-      <c r="P34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q34" s="2"/>
-      <c r="R34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AG34" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK34" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="C35" s="2"/>
-      <c r="D35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E35" s="2"/>
-      <c r="F35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K35" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L35" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
-      <c r="P35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q35" s="2"/>
-      <c r="R35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="C36" s="2"/>
-      <c r="D36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E36" s="2"/>
-      <c r="F36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K36" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
-      <c r="P36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q36" s="2"/>
-      <c r="R36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AG36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK36" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="C37" s="2"/>
-      <c r="D37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E37" s="2"/>
-      <c r="F37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="G37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K37" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O37" s="2"/>
-      <c r="P37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q37" s="2"/>
-      <c r="R37" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="S37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AG37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="C38" s="2"/>
-      <c r="D38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E38" s="2"/>
-      <c r="F38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K38" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="L38" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
-      <c r="P38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q38" s="2"/>
-      <c r="R38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="D39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E39" s="2"/>
-      <c r="F39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K39" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
-      <c r="P39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q39" s="2"/>
-      <c r="R39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AG39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="C40" s="2"/>
-      <c r="D40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E40" s="2"/>
-      <c r="F40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K40" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
-      <c r="P40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q40" s="2"/>
-      <c r="R40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="C41" s="2"/>
-      <c r="D41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E41" s="2"/>
-      <c r="F41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K41" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
-      <c r="P41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q41" s="2"/>
-      <c r="R41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AG41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="C42" s="2"/>
-      <c r="D42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E42" s="2"/>
-      <c r="F42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="G42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K42" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O42" s="2"/>
-      <c r="P42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q42" s="2"/>
-      <c r="R42" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="S42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AG42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK42" t="s" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="C43" s="2"/>
-      <c r="D43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E43" s="2"/>
-      <c r="F43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K43" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
-      <c r="P43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q43" s="2"/>
-      <c r="R43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X43" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y43" s="2"/>
-      <c r="Z43" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="C44" s="2"/>
-      <c r="D44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E44" s="2"/>
-      <c r="F44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="G44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K44" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O44" s="2"/>
-      <c r="P44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q44" s="2"/>
-      <c r="R44" t="s" s="2">
-        <v>3</v>
-      </c>
-      <c r="S44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="C45" s="2"/>
-      <c r="D45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E45" s="2"/>
-      <c r="F45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K45" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
-      <c r="P45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q45" s="2"/>
-      <c r="R45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AK45" t="s" s="2">
         <v>100</v>
       </c>
     </row>

--- a/nr-update-missing-fields/ig/StructureDefinition-as-ext-authorization.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-ext-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T09:13:15+00:00</t>
+    <t>2024-07-17T12:12:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-missing-fields/ig/StructureDefinition-as-ext-authorization.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-ext-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:12:47+00:00</t>
+    <t>2024-07-17T15:12:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-missing-fields/ig/StructureDefinition-as-ext-authorization.xlsx
+++ b/nr-update-missing-fields/ig/StructureDefinition-as-ext-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T15:12:21+00:00</t>
+    <t>2024-07-25T07:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
